--- a/artfynd/A 1827-2025 artfynd.xlsx
+++ b/artfynd/A 1827-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108176237</v>
+        <v>108176273</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>824863.300863351</v>
+        <v>824863</v>
       </c>
       <c r="R2" t="n">
-        <v>7382334.537576487</v>
+        <v>7382334</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108176273</v>
+        <v>108176237</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>824863.300863351</v>
+        <v>824863</v>
       </c>
       <c r="R3" t="n">
-        <v>7382334.537576487</v>
+        <v>7382334</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,16 +894,11 @@
         <v>108176297</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -942,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>824863.300863351</v>
+        <v>824863</v>
       </c>
       <c r="R4" t="n">
-        <v>7382334.537576487</v>
+        <v>7382334</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,6 +996,114 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>108176872</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvarnån, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>824794</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7382327</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1827-2025 artfynd.xlsx
+++ b/artfynd/A 1827-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108176273</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108176237</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108176297</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,8 +1124,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108176872</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>